--- a/tools/importer/reports/import-services-page.report.xlsx
+++ b/tools/importer/reports/import-services-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>services-page</t>
   </si>
   <si>
-    <t>2026-05-01T18:05:52.917Z</t>
+    <t>2026-05-01T18:58:44.209Z</t>
   </si>
   <si>
     <t>Family Office Services | Accounting &amp; Advisory Services</t>

--- a/tools/importer/reports/import-services-page.report.xlsx
+++ b/tools/importer/reports/import-services-page.report.xlsx
@@ -40,7 +40,7 @@
     <t>services/family-office-services.report.json</t>
   </si>
   <si>
-    <t>["hero-split","columns-featured","columns-featured","columns-highlight","quote","stats","carousel","cards-featured","cards-insights"]</t>
+    <t>["hero-split","columns-featured","columns-featured","columns-highlight","quote","stats","carousel-contacts","cards-featured","cards-insights"]</t>
   </si>
   <si>
     <t>services/family-office-services</t>
@@ -52,7 +52,7 @@
     <t>services-page</t>
   </si>
   <si>
-    <t>2026-05-01T18:58:44.209Z</t>
+    <t>2026-05-02T01:56:19.067Z</t>
   </si>
   <si>
     <t>Family Office Services | Accounting &amp; Advisory Services</t>
